--- a/mlef_pipeline/results/OS_24/IO_ONLY/RWD_DP/rwd-only/results.xlsx
+++ b/mlef_pipeline/results/OS_24/IO_ONLY/RWD_DP/rwd-only/results.xlsx
@@ -473,7 +473,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.65 ± 0.07</t>
+          <t>0.64 ± 0.07</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.64 ± 0.19</t>
+          <t>0.64 ± 0.18</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
